--- a/information_forms/022_covid_19_daily_status_update_form--information_forms.xlsx
+++ b/information_forms/022_covid_19_daily_status_update_form--information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +813,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'fully_vaccinated'}</t>
+          <t>fully_vaccinated</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Fully Vaccinated'}</t>
+          <t>Fully Vaccinated</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'partly_vaccinated'}</t>
+          <t>partly_vaccinated</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Partly Vaccinated'}</t>
+          <t>Partly Vaccinated</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_vaccinated'}</t>
+          <t>not_vaccinated</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not Vaccinated'}</t>
+          <t>Not Vaccinated</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'declined_vaccination'}</t>
+          <t>declined_vaccination</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Declined Vaccination'}</t>
+          <t>Declined Vaccination</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'active_case'}</t>
+          <t>active_case</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Active Case'}</t>
+          <t>Active Case</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'recovered'}</t>
+          <t>recovered</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Recovered'}</t>
+          <t>Recovered</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'deceased'}</t>
+          <t>deceased</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Deceased'}</t>
+          <t>Deceased</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'inconclusive'}</t>
+          <t>inconclusive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Inconclusive'}</t>
+          <t>Inconclusive</t>
         </is>
       </c>
     </row>
